--- a/backend/tests/Fixtures/results_update_synthetic.xlsx
+++ b/backend/tests/Fixtures/results_update_synthetic.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="18">
   <si>
     <t>JNTU No</t>
   </si>
@@ -63,6 +63,12 @@
   </si>
   <si>
     <t>Nobody</t>
+  </si>
+  <si>
+    <t>24341D5701</t>
+  </si>
+  <si>
+    <t>Om Test</t>
   </si>
 </sst>
 </file>
@@ -402,7 +408,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -498,6 +504,23 @@
         <v>0</v>
       </c>
       <c r="E6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7">
+        <v>8.1</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7" t="s">
         <v>7</v>
       </c>
     </row>
